--- a/django application/Saransha/single_profile_publications.xlsx
+++ b/django application/Saransha/single_profile_publications.xlsx
@@ -160,7 +160,7 @@
     <t>KH Susheelamma and Smriti Gururaj</t>
   </si>
   <si>
-    <t>2025-11-28</t>
+    <t>2026-01-02</t>
   </si>
 </sst>
 </file>
